--- a/test.xlsx
+++ b/test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clarivate-my.sharepoint.com/personal/mitsuhiro_matsuo_clarivate_com/Documents/Desktop/APP_IPC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50E23B48-E224-4A4D-841E-87B4DAF62E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{50E23B48-E224-4A4D-841E-87B4DAF62E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D638EAA-3848-4670-ADCE-1EFD59A25A25}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0482642B-C436-4CB2-ABF5-45C3BFA39B29}"/>
+    <workbookView minimized="1" xWindow="330" yWindow="330" windowWidth="19190" windowHeight="10070" xr2:uid="{0482642B-C436-4CB2-ABF5-45C3BFA39B29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,22 +65,24 @@
     <t>F21V 29/02</t>
   </si>
   <si>
+    <t>G03B  7/08</t>
+  </si>
+  <si>
+    <t>G03B  7/16</t>
+  </si>
+  <si>
+    <t>G03F  1/00</t>
+  </si>
+  <si>
+    <t>H01L21/027</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>G01N 21/35</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>G03B  7/00</t>
-  </si>
-  <si>
-    <t>G03B  7/08</t>
-  </si>
-  <si>
-    <t>G03B  7/16</t>
-  </si>
-  <si>
-    <t>G03F  1/00</t>
-  </si>
-  <si>
-    <t>H01L21/027</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -510,32 +512,32 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
